--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/KANSAS_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/KANSAS_2021.xlsx
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C135">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C214">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C221">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C488">
